--- a/dataset_t6_grouped/results2/G2/G2_T1448_W0038F0001T0006Z000C1N50_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T1448_W0038F0001T0006Z000C1N50_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>14.82455160098924</v>
+        <v>2.408989635160752</v>
       </c>
       <c r="D2" t="n">
-        <v>17.71754284175114</v>
+        <v>2.87910071178456</v>
       </c>
       <c r="E2" t="n">
-        <v>13.19860329257052</v>
+        <v>2.144773035042709</v>
       </c>
       <c r="F2" t="n">
-        <v>11.60410798978104</v>
+        <v>1.88566754833942</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>35.61594526963383</v>
+        <v>5.787591106315497</v>
       </c>
       <c r="D3" t="n">
-        <v>35.16096528030369</v>
+        <v>5.71365685804935</v>
       </c>
       <c r="E3" t="n">
-        <v>13.19860329257052</v>
+        <v>2.144773035042709</v>
       </c>
       <c r="F3" t="n">
-        <v>11.60410798978104</v>
+        <v>1.88566754833942</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>33.40983786935921</v>
+        <v>5.429098653770872</v>
       </c>
       <c r="D4" t="n">
-        <v>31.58216743744439</v>
+        <v>5.132102208584714</v>
       </c>
       <c r="E4" t="n">
-        <v>13.19860329257052</v>
+        <v>2.144773035042709</v>
       </c>
       <c r="F4" t="n">
-        <v>11.60410798978104</v>
+        <v>1.88566754833942</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>46.24589687002186</v>
+        <v>7.514958241378553</v>
       </c>
       <c r="D5" t="n">
-        <v>47.80754099994046</v>
+        <v>7.768725412490325</v>
       </c>
       <c r="E5" t="n">
-        <v>13.19860329257052</v>
+        <v>2.144773035042709</v>
       </c>
       <c r="F5" t="n">
-        <v>11.60410798978104</v>
+        <v>1.88566754833942</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>39.08817457860633</v>
+        <v>6.351828369023528</v>
       </c>
       <c r="D6" t="n">
-        <v>36.78661132557673</v>
+        <v>5.977824340406219</v>
       </c>
       <c r="E6" t="n">
-        <v>13.19860329257052</v>
+        <v>2.144773035042709</v>
       </c>
       <c r="F6" t="n">
-        <v>11.60410798978104</v>
+        <v>1.88566754833942</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>31.0616999012458</v>
+        <v>5.047526233952443</v>
       </c>
       <c r="D7" t="n">
-        <v>29.09702011804204</v>
+        <v>4.728265769181832</v>
       </c>
       <c r="E7" t="n">
-        <v>13.19860329257052</v>
+        <v>2.144773035042709</v>
       </c>
       <c r="F7" t="n">
-        <v>11.60410798978104</v>
+        <v>1.88566754833942</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>42.79393742013986</v>
+        <v>6.954014830772728</v>
       </c>
       <c r="D8" t="n">
-        <v>44.98229136485725</v>
+        <v>7.309622346789303</v>
       </c>
       <c r="E8" t="n">
-        <v>13.19860329257052</v>
+        <v>2.144773035042709</v>
       </c>
       <c r="F8" t="n">
-        <v>11.60410798978104</v>
+        <v>1.88566754833942</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>41.35457196928611</v>
+        <v>6.720117945008992</v>
       </c>
       <c r="D9" t="n">
-        <v>17.97579974309217</v>
+        <v>2.921067458252478</v>
       </c>
       <c r="E9" t="n">
-        <v>13.19860329257052</v>
+        <v>2.144773035042709</v>
       </c>
       <c r="F9" t="n">
-        <v>11.60410798978104</v>
+        <v>1.88566754833942</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>42.17282945720009</v>
+        <v>6.853084786795015</v>
       </c>
       <c r="D10" t="n">
-        <v>36.47257236823652</v>
+        <v>5.926793009838435</v>
       </c>
       <c r="E10" t="n">
-        <v>13.19860329257052</v>
+        <v>2.144773035042709</v>
       </c>
       <c r="F10" t="n">
-        <v>11.60410798978104</v>
+        <v>1.88566754833942</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>25.12582103759802</v>
+        <v>4.082945918609678</v>
       </c>
       <c r="D11" t="n">
-        <v>17.06875171640416</v>
+        <v>2.773672153915677</v>
       </c>
       <c r="E11" t="n">
-        <v>13.19860329257052</v>
+        <v>2.144773035042709</v>
       </c>
       <c r="F11" t="n">
-        <v>11.60410798978104</v>
+        <v>1.88566754833942</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>72.29463433479313</v>
+        <v>11.74787807940388</v>
       </c>
       <c r="D12" t="n">
-        <v>35.56714122908119</v>
+        <v>5.779660449725695</v>
       </c>
       <c r="E12" t="n">
-        <v>13.19860329257052</v>
+        <v>2.144773035042709</v>
       </c>
       <c r="F12" t="n">
-        <v>11.60410798978104</v>
+        <v>1.88566754833942</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>31.43767627692923</v>
+        <v>5.108622395001</v>
       </c>
       <c r="D13" t="n">
-        <v>8.642900465182475</v>
+        <v>1.404471325592152</v>
       </c>
       <c r="E13" t="n">
-        <v>13.19860329257052</v>
+        <v>2.144773035042709</v>
       </c>
       <c r="F13" t="n">
-        <v>11.60410798978104</v>
+        <v>1.88566754833942</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>46.53717693376523</v>
+        <v>7.56229125173685</v>
       </c>
       <c r="D14" t="n">
-        <v>22.45133275195816</v>
+        <v>3.6483415721932</v>
       </c>
       <c r="E14" t="n">
-        <v>13.19860329257052</v>
+        <v>2.144773035042709</v>
       </c>
       <c r="F14" t="n">
-        <v>11.60410798978104</v>
+        <v>1.88566754833942</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>22.10330270344709</v>
+        <v>3.591786689310152</v>
       </c>
       <c r="D15" t="n">
-        <v>13.77459202506664</v>
+        <v>2.238371204073328</v>
       </c>
       <c r="E15" t="n">
-        <v>13.19860329257052</v>
+        <v>2.144773035042709</v>
       </c>
       <c r="F15" t="n">
-        <v>11.60410798978104</v>
+        <v>1.88566754833942</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
